--- a/bin/pending_rfrs_source.xlsx
+++ b/bin/pending_rfrs_source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\IQA DATA\iqa-data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C9153D-3168-4119-A827-DB41841E26AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFCF046-D642-4B04-BB8D-57D57CCD76F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{CD4E6399-B2A4-4637-80A1-F963F6DA3DE5}"/>
+    <workbookView xWindow="1965" yWindow="2490" windowWidth="24960" windowHeight="11430" xr2:uid="{CD4E6399-B2A4-4637-80A1-F963F6DA3DE5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Year</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>FY03-04</t>
+  </si>
+  <si>
+    <t>FY24</t>
   </si>
 </sst>
 </file>
@@ -193,9 +196,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -233,7 +236,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -339,7 +342,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -481,7 +484,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -489,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD143C0-3FFE-403D-8194-F73A02D5ED39}">
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.140625" customWidth="1"/>
@@ -963,6 +966,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/bin/pending_rfrs_source.xlsx
+++ b/bin/pending_rfrs_source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFCF046-D642-4B04-BB8D-57D57CCD76F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27200958-5656-46A4-8463-28A7A9DE9BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1965" yWindow="2490" windowWidth="24960" windowHeight="11430" xr2:uid="{CD4E6399-B2A4-4637-80A1-F963F6DA3DE5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CD4E6399-B2A4-4637-80A1-F963F6DA3DE5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Year</t>
   </si>
@@ -115,6 +118,9 @@
   </si>
   <si>
     <t>FY24</t>
+  </si>
+  <si>
+    <t>FY25</t>
   </si>
 </sst>
 </file>
@@ -492,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD143C0-3FFE-403D-8194-F73A02D5ED39}">
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.140625" customWidth="1"/>
@@ -986,6 +992,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/bin/pending_rfrs_source.xlsx
+++ b/bin/pending_rfrs_source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27200958-5656-46A4-8463-28A7A9DE9BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E917B5D4-4068-4A4E-9070-61D62B6F5463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CD4E6399-B2A4-4637-80A1-F963F6DA3DE5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Year</t>
   </si>
@@ -84,21 +84,6 @@
     <t>FY18</t>
   </si>
   <si>
-    <t>FY19</t>
-  </si>
-  <si>
-    <t>FY20</t>
-  </si>
-  <si>
-    <t>FY21</t>
-  </si>
-  <si>
-    <t>FY22</t>
-  </si>
-  <si>
-    <t>FY23</t>
-  </si>
-  <si>
     <t>Correction</t>
   </si>
   <si>
@@ -115,12 +100,6 @@
   </si>
   <si>
     <t>FY03-04</t>
-  </si>
-  <si>
-    <t>FY24</t>
-  </si>
-  <si>
-    <t>FY25</t>
   </si>
 </sst>
 </file>
@@ -498,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD143C0-3FFE-403D-8194-F73A02D5ED39}">
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.140625" customWidth="1"/>
@@ -513,24 +492,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -872,146 +851,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
